--- a/output/Test V7 Fix - 2026-04-14.xlsx
+++ b/output/Test V7 Fix - 2026-04-14.xlsx
@@ -38,13 +38,13 @@
     <t>Fecha</t>
   </si>
   <si>
+    <t>FechaCompleto</t>
+  </si>
+  <si>
+    <t>Archivado</t>
+  </si>
+  <si>
     <t>Completo</t>
-  </si>
-  <si>
-    <t>Archivado</t>
-  </si>
-  <si>
-    <t>Column11</t>
   </si>
   <si>
     <t>Factura</t>
@@ -182,9 +182,9 @@
     <tableColumn id="6" name="UnidadOrganica" totalsRowFunction="average"/>
     <tableColumn id="7" name="Oficina" totalsRowFunction="average"/>
     <tableColumn id="8" name="Fecha" totalsRowFunction="average"/>
-    <tableColumn id="9" name="Completo" totalsRowFunction="average"/>
+    <tableColumn id="9" name="FechaCompleto" totalsRowFunction="average"/>
     <tableColumn id="10" name="Archivado" totalsRowFunction="average"/>
-    <tableColumn id="11" name="Column11" totalsRowFunction="average"/>
+    <tableColumn id="11" name="Completo" totalsRowFunction="average"/>
     <tableColumn id="12" name="Factura" totalsRowFunction="average"/>
     <tableColumn id="13" name="NumFactura" totalsRowFunction="average"/>
     <tableColumn id="14" name="ImporteFactura" totalsRowFunction="average"/>
@@ -230,7 +230,7 @@
     <col min="6" max="6" width="17.0667157854353" customWidth="1"/>
     <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.524770464216" customWidth="1"/>
+    <col min="9" max="9" width="16.6697671072824" customWidth="1"/>
     <col min="10" max="10" width="11.7703061785017" customWidth="1"/>
     <col min="11" max="11" width="11.524770464216" customWidth="1"/>
     <col min="12" max="12" width="9.52774701799665" customWidth="1"/>

--- a/output/Test V7 Fix - 2026-04-14.xlsx
+++ b/output/Test V7 Fix - 2026-04-14.xlsx
@@ -136,7 +136,7 @@
   <fonts count="1">
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -218,48 +218,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <dimension ref="A1:AL1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.4607827322824" customWidth="1"/>
-    <col min="3" max="3" width="10.2981153215681" customWidth="1"/>
-    <col min="4" max="4" width="11.103267124721" customWidth="1"/>
-    <col min="5" max="5" width="9.16967337472098" customWidth="1"/>
-    <col min="6" max="6" width="17.0667157854353" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="16.6697671072824" customWidth="1"/>
-    <col min="10" max="10" width="11.7703061785017" customWidth="1"/>
-    <col min="11" max="11" width="11.524770464216" customWidth="1"/>
-    <col min="12" max="12" width="9.52774701799665" customWidth="1"/>
-    <col min="13" max="13" width="13.7785840715681" customWidth="1"/>
-    <col min="14" max="14" width="16.6155439104353" customWidth="1"/>
-    <col min="15" max="15" width="20.8796822684152" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" customWidth="1"/>
-    <col min="17" max="17" width="24.6087559291295" customWidth="1"/>
-    <col min="18" max="18" width="10.8894468035017" customWidth="1"/>
-    <col min="19" max="19" width="12.1416789463588" customWidth="1"/>
-    <col min="20" max="20" width="26.9433898925781" customWidth="1"/>
-    <col min="21" max="21" width="15.8932604108538" customWidth="1"/>
-    <col min="22" max="22" width="13.2527280535017" customWidth="1"/>
-    <col min="23" max="23" width="15.7469613211496" customWidth="1"/>
-    <col min="24" max="24" width="18.7394278390067" customWidth="1"/>
-    <col min="25" max="25" width="18.7803508213588" customWidth="1"/>
-    <col min="26" max="26" width="9.140625" customWidth="1"/>
-    <col min="27" max="27" width="11.189204624721" customWidth="1"/>
-    <col min="28" max="28" width="14.3678697858538" customWidth="1"/>
-    <col min="29" max="29" width="11.7304066249302" customWidth="1"/>
-    <col min="30" max="30" width="10.9978921072824" customWidth="1"/>
-    <col min="31" max="31" width="9.140625" customWidth="1"/>
-    <col min="32" max="32" width="18.722036089216" customWidth="1"/>
-    <col min="33" max="33" width="23.6194501604353" customWidth="1"/>
-    <col min="34" max="34" width="9.140625" customWidth="1"/>
-    <col min="35" max="35" width="16.6267983572824" customWidth="1"/>
-    <col min="36" max="36" width="9.140625" customWidth="1"/>
-    <col min="37" max="37" width="9.140625" customWidth="1"/>
-    <col min="38" max="38" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.194204057966" customWidth="1"/>
+    <col min="2" max="2" width="17.194204057966" customWidth="1"/>
+    <col min="3" max="3" width="17.194204057966" customWidth="1"/>
+    <col min="4" max="4" width="17.194204057966" customWidth="1"/>
+    <col min="5" max="5" width="17.194204057966" customWidth="1"/>
+    <col min="6" max="6" width="17.194204057966" customWidth="1"/>
+    <col min="7" max="7" width="17.194204057966" customWidth="1"/>
+    <col min="8" max="8" width="17.194204057966" customWidth="1"/>
+    <col min="9" max="9" width="17.194204057966" customWidth="1"/>
+    <col min="10" max="10" width="17.194204057966" customWidth="1"/>
+    <col min="11" max="11" width="17.194204057966" customWidth="1"/>
+    <col min="12" max="12" width="17.194204057966" customWidth="1"/>
+    <col min="13" max="13" width="17.194204057966" customWidth="1"/>
+    <col min="14" max="14" width="17.194204057966" customWidth="1"/>
+    <col min="15" max="15" width="20.4914136614118" customWidth="1"/>
+    <col min="16" max="16" width="17.194204057966" customWidth="1"/>
+    <col min="17" max="17" width="24.0217939104353" customWidth="1"/>
+    <col min="18" max="18" width="17.194204057966" customWidth="1"/>
+    <col min="19" max="19" width="17.194204057966" customWidth="1"/>
+    <col min="20" max="20" width="26.2613198416574" customWidth="1"/>
+    <col min="21" max="21" width="17.194204057966" customWidth="1"/>
+    <col min="22" max="22" width="17.194204057966" customWidth="1"/>
+    <col min="23" max="23" width="17.194204057966" customWidth="1"/>
+    <col min="24" max="24" width="17.8082297188895" customWidth="1"/>
+    <col min="25" max="25" width="18.1103973388672" customWidth="1"/>
+    <col min="26" max="26" width="17.194204057966" customWidth="1"/>
+    <col min="27" max="27" width="17.194204057966" customWidth="1"/>
+    <col min="28" max="28" width="17.194204057966" customWidth="1"/>
+    <col min="29" max="29" width="17.194204057966" customWidth="1"/>
+    <col min="30" max="30" width="17.194204057966" customWidth="1"/>
+    <col min="31" max="31" width="17.194204057966" customWidth="1"/>
+    <col min="32" max="32" width="18.3479723249163" customWidth="1"/>
+    <col min="33" max="33" width="22.9961874825614" customWidth="1"/>
+    <col min="34" max="34" width="17.194204057966" customWidth="1"/>
+    <col min="35" max="35" width="17.194204057966" customWidth="1"/>
+    <col min="36" max="36" width="17.194204057966" customWidth="1"/>
+    <col min="37" max="37" width="17.194204057966" customWidth="1"/>
+    <col min="38" max="38" width="17.194204057966" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -378,11 +378,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <headerFooter/>
   <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to My Noncommercial organization under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>